--- a/artfynd/A 14443-2025 artfynd.xlsx
+++ b/artfynd/A 14443-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123967167</v>
+        <v>123966171</v>
       </c>
       <c r="B2" t="n">
-        <v>56700</v>
+        <v>90955</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,45 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Porsmyran V, Dlr</t>
+          <t>Porsmyran. V, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>507868</v>
+        <v>507676</v>
       </c>
       <c r="R2" t="n">
-        <v>6707394</v>
+        <v>6707387</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:22</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Under tall.</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123966171</v>
+        <v>123967167</v>
       </c>
       <c r="B3" t="n">
-        <v>90955</v>
+        <v>56700</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,37 +803,45 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Porsmyran. V, Dlr</t>
+          <t>Porsmyran V, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507676</v>
+        <v>507868</v>
       </c>
       <c r="R3" t="n">
-        <v>6707387</v>
+        <v>6707394</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,7 +880,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Under tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123968187</v>
+        <v>123965543</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
+        <v>92271</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,38 +924,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Porsmyran. V, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507735</v>
+        <v>507676</v>
       </c>
       <c r="R4" t="n">
-        <v>6707521</v>
+        <v>6707387</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -987,7 +996,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +1006,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>G:a fk</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,14 +1031,14 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123982500</v>
+        <v>123982555</v>
       </c>
       <c r="B5" t="n">
         <v>56700</v>
@@ -1057,12 +1071,20 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>dödad av predator</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1072,10 +1094,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507842</v>
+        <v>507817</v>
       </c>
       <c r="R5" t="n">
-        <v>6707423</v>
+        <v>6707465</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1107,7 +1129,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1117,12 +1139,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Under äldre tall</t>
+          <t>Slagen tjäderhöna möjligen på tänkt bogrop intill tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,10 +1171,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123982563</v>
+        <v>123967232</v>
       </c>
       <c r="B6" t="n">
-        <v>78788</v>
+        <v>78789</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,16 +1187,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1183,19 +1205,16 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Porsmyran V, Dlr</t>
+          <t>Porsmyran. V, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>507817</v>
       </c>
       <c r="R6" t="n">
-        <v>6707465</v>
+        <v>6707436</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1227,7 +1246,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1256,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,7 +1265,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1258,17 +1276,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123967232</v>
+        <v>123965450</v>
       </c>
       <c r="B7" t="n">
-        <v>78789</v>
+        <v>78788</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,16 +1299,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1305,10 +1323,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507817</v>
+        <v>507676</v>
       </c>
       <c r="R7" t="n">
-        <v>6707436</v>
+        <v>6707387</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1340,7 +1358,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,7 +1368,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,17 +1388,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123968246</v>
+        <v>123968070</v>
       </c>
       <c r="B8" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,39 +1411,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Porsmyran. V, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507683</v>
+        <v>507735</v>
       </c>
       <c r="R8" t="n">
-        <v>6707604</v>
+        <v>6707521</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1457,7 +1470,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1467,12 +1480,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Möjlig födosök tretåig.</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1499,10 +1507,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123965450</v>
+        <v>123982500</v>
       </c>
       <c r="B9" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1511,38 +1519,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Porsmyran. V, Dlr</t>
+          <t>Porsmyran V, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507676</v>
+        <v>507842</v>
       </c>
       <c r="R9" t="n">
-        <v>6707387</v>
+        <v>6707423</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1574,7 +1590,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1584,7 +1600,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Under äldre tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1611,10 +1632,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123965543</v>
+        <v>123967723</v>
       </c>
       <c r="B10" t="n">
-        <v>92271</v>
+        <v>57491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1623,35 +1644,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1660,10 +1677,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>507676</v>
+        <v>507804</v>
       </c>
       <c r="R10" t="n">
-        <v>6707387</v>
+        <v>6707453</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1695,7 +1712,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1705,12 +1722,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:37</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>G:a fk</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1737,10 +1749,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123982555</v>
+        <v>123982563</v>
       </c>
       <c r="B11" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1749,43 +1761,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>dödad av predator</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1828,7 +1827,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1838,12 +1837,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:40</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Slagen tjäderhöna möjligen på tänkt bogrop intill tall.</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1852,6 +1846,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1870,7 +1865,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123967723</v>
+        <v>123968246</v>
       </c>
       <c r="B12" t="n">
         <v>57491</v>
@@ -1915,10 +1910,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>507804</v>
+        <v>507683</v>
       </c>
       <c r="R12" t="n">
-        <v>6707453</v>
+        <v>6707604</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1963,6 +1958,11 @@
           <t>11:50</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Möjlig födosök tretåig.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1984,6 +1984,1409 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123995923</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Porsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>507824</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6707424</v>
+      </c>
+      <c r="S13" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>123995875</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Porsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>507841</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6707427</v>
+      </c>
+      <c r="S14" t="n">
+        <v>50</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>123995953</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Porsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>507837</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6707412</v>
+      </c>
+      <c r="S15" t="n">
+        <v>50</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>123995965</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Porsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>507831</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6707436</v>
+      </c>
+      <c r="S16" t="n">
+        <v>50</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>123995839</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Porsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>507890</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6707384</v>
+      </c>
+      <c r="S17" t="n">
+        <v>50</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>123996131</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Porsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>507768</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6707485</v>
+      </c>
+      <c r="S18" t="n">
+        <v>50</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>123995815</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Porsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>507867</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6707382</v>
+      </c>
+      <c r="S19" t="n">
+        <v>50</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>123996113</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Porsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>507774</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6707494</v>
+      </c>
+      <c r="S20" t="n">
+        <v>50</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>123996079</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98079</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Porsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>507858</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6707444</v>
+      </c>
+      <c r="S21" t="n">
+        <v>50</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>123996098</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Porsmyram, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>507760</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6707500</v>
+      </c>
+      <c r="S22" t="n">
+        <v>50</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>123996142</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Porsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>507697</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6707549</v>
+      </c>
+      <c r="S23" t="n">
+        <v>50</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>123999506</v>
+      </c>
+      <c r="B24" t="n">
+        <v>5176</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Porsmyran V, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>507817</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6707434</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>123996155</v>
+      </c>
+      <c r="B25" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Porsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>507675</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6707591</v>
+      </c>
+      <c r="S25" t="n">
+        <v>50</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14443-2025 artfynd.xlsx
+++ b/artfynd/A 14443-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123967167</v>
+        <v>123982500</v>
       </c>
       <c r="B3" t="n">
         <v>56700</v>
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507868</v>
+        <v>507842</v>
       </c>
       <c r="R3" t="n">
-        <v>6707394</v>
+        <v>6707423</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Under tall.</t>
+          <t>Under äldre tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123965543</v>
+        <v>123968070</v>
       </c>
       <c r="B4" t="n">
-        <v>92271</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,47 +924,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Porsmyran. V, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507676</v>
+        <v>507735</v>
       </c>
       <c r="R4" t="n">
-        <v>6707387</v>
+        <v>6707521</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -996,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1006,12 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:37</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>G:a fk</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123982555</v>
+        <v>123965543</v>
       </c>
       <c r="B5" t="n">
-        <v>56700</v>
+        <v>92271</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1054,50 +1040,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>dödad av predator</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Porsmyran V, Dlr</t>
+          <t>Porsmyran. V, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507817</v>
+        <v>507676</v>
       </c>
       <c r="R5" t="n">
-        <v>6707465</v>
+        <v>6707387</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1129,7 +1108,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1139,12 +1118,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Slagen tjäderhöna möjligen på tänkt bogrop intill tall.</t>
+          <t>G:a fk</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1171,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123967232</v>
+        <v>123968246</v>
       </c>
       <c r="B6" t="n">
-        <v>78789</v>
+        <v>57491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1187,34 +1166,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>230405</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Porsmyran. V, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>507817</v>
+        <v>507683</v>
       </c>
       <c r="R6" t="n">
-        <v>6707436</v>
+        <v>6707604</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1246,7 +1230,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1256,7 +1240,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Möjlig födosök tretåig.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1276,17 +1265,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123965450</v>
+        <v>123967723</v>
       </c>
       <c r="B7" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1299,34 +1288,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Porsmyran. V, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507676</v>
+        <v>507804</v>
       </c>
       <c r="R7" t="n">
-        <v>6707387</v>
+        <v>6707453</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1358,7 +1352,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1368,7 +1362,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1395,10 +1389,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123968070</v>
+        <v>123967232</v>
       </c>
       <c r="B8" t="n">
-        <v>78788</v>
+        <v>78789</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1411,16 +1405,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1435,10 +1429,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507735</v>
+        <v>507817</v>
       </c>
       <c r="R8" t="n">
-        <v>6707521</v>
+        <v>6707436</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1470,7 +1464,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1480,7 +1474,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1500,14 +1494,14 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123982500</v>
+        <v>123967167</v>
       </c>
       <c r="B9" t="n">
         <v>56700</v>
@@ -1555,13 +1549,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507842</v>
+        <v>507868</v>
       </c>
       <c r="R9" t="n">
-        <v>6707423</v>
+        <v>6707394</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1590,7 +1584,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1600,12 +1594,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Under äldre tall</t>
+          <t>Under tall.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1632,10 +1626,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123967723</v>
+        <v>123982563</v>
       </c>
       <c r="B10" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1648,39 +1642,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Porsmyran. V, Dlr</t>
+          <t>Porsmyran V, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>507804</v>
+        <v>507817</v>
       </c>
       <c r="R10" t="n">
-        <v>6707453</v>
+        <v>6707465</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1712,7 +1704,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1722,7 +1714,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1731,6 +1723,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1749,10 +1742,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123982563</v>
+        <v>123982555</v>
       </c>
       <c r="B11" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1761,30 +1754,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>dödad av predator</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1827,7 +1833,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1837,7 +1843,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Slagen tjäderhöna möjligen på tänkt bogrop intill tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1846,7 +1857,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1865,10 +1875,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123968246</v>
+        <v>123965450</v>
       </c>
       <c r="B12" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1881,39 +1891,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Porsmyran. V, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>507683</v>
+        <v>507676</v>
       </c>
       <c r="R12" t="n">
-        <v>6707604</v>
+        <v>6707387</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1945,7 +1950,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1955,12 +1960,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Möjlig födosök tretåig.</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1987,7 +1987,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123995923</v>
+        <v>123996113</v>
       </c>
       <c r="B13" t="n">
         <v>78788</v>
@@ -2030,10 +2030,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>507824</v>
+        <v>507774</v>
       </c>
       <c r="R13" t="n">
-        <v>6707424</v>
+        <v>6707494</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -2093,7 +2093,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123995875</v>
+        <v>123995839</v>
       </c>
       <c r="B14" t="n">
         <v>78788</v>
@@ -2136,10 +2136,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>507841</v>
+        <v>507890</v>
       </c>
       <c r="R14" t="n">
-        <v>6707427</v>
+        <v>6707384</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2199,7 +2199,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123995953</v>
+        <v>123995923</v>
       </c>
       <c r="B15" t="n">
         <v>78788</v>
@@ -2242,10 +2242,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>507837</v>
+        <v>507824</v>
       </c>
       <c r="R15" t="n">
-        <v>6707412</v>
+        <v>6707424</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2305,10 +2305,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123995965</v>
+        <v>123996079</v>
       </c>
       <c r="B16" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2317,30 +2317,39 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2348,10 +2357,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>507831</v>
+        <v>507858</v>
       </c>
       <c r="R16" t="n">
-        <v>6707436</v>
+        <v>6707444</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2411,7 +2420,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123995839</v>
+        <v>123996155</v>
       </c>
       <c r="B17" t="n">
         <v>78788</v>
@@ -2454,10 +2463,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>507890</v>
+        <v>507675</v>
       </c>
       <c r="R17" t="n">
-        <v>6707384</v>
+        <v>6707591</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2484,12 +2493,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2517,7 +2526,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123996131</v>
+        <v>123995815</v>
       </c>
       <c r="B18" t="n">
         <v>78788</v>
@@ -2560,10 +2569,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>507768</v>
+        <v>507867</v>
       </c>
       <c r="R18" t="n">
-        <v>6707485</v>
+        <v>6707382</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2623,7 +2632,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123995815</v>
+        <v>123995953</v>
       </c>
       <c r="B19" t="n">
         <v>78788</v>
@@ -2666,10 +2675,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>507867</v>
+        <v>507837</v>
       </c>
       <c r="R19" t="n">
-        <v>6707382</v>
+        <v>6707412</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2729,10 +2738,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123996113</v>
+        <v>123999506</v>
       </c>
       <c r="B20" t="n">
-        <v>78788</v>
+        <v>5176</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2741,44 +2750,50 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Porsmyran, Dlr</t>
+          <t>Porsmyran V, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>507774</v>
+        <v>507817</v>
       </c>
       <c r="R20" t="n">
-        <v>6707494</v>
+        <v>6707434</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2805,9 +2820,19 @@
           <t>2025-04-11</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2823,22 +2848,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123996079</v>
+        <v>123996142</v>
       </c>
       <c r="B21" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2847,39 +2872,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2887,10 +2903,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>507858</v>
+        <v>507697</v>
       </c>
       <c r="R21" t="n">
-        <v>6707444</v>
+        <v>6707549</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2950,7 +2966,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123996098</v>
+        <v>123995965</v>
       </c>
       <c r="B22" t="n">
         <v>78788</v>
@@ -2989,14 +3005,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Porsmyram, Dlr</t>
+          <t>Porsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>507760</v>
+        <v>507831</v>
       </c>
       <c r="R22" t="n">
-        <v>6707500</v>
+        <v>6707436</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -3056,7 +3072,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123996142</v>
+        <v>123996131</v>
       </c>
       <c r="B23" t="n">
         <v>78788</v>
@@ -3099,10 +3115,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>507697</v>
+        <v>507768</v>
       </c>
       <c r="R23" t="n">
-        <v>6707549</v>
+        <v>6707485</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3162,10 +3178,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123999506</v>
+        <v>123995875</v>
       </c>
       <c r="B24" t="n">
-        <v>5176</v>
+        <v>78788</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3174,50 +3190,44 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Porsmyran V, Dlr</t>
+          <t>Porsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>507817</v>
+        <v>507841</v>
       </c>
       <c r="R24" t="n">
-        <v>6707434</v>
+        <v>6707427</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3244,19 +3254,9 @@
           <t>2025-04-11</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>11:30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3272,19 +3272,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123996155</v>
+        <v>123996098</v>
       </c>
       <c r="B25" t="n">
         <v>78788</v>
@@ -3323,14 +3323,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Porsmyran, Dlr</t>
+          <t>Porsmyram, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>507675</v>
+        <v>507760</v>
       </c>
       <c r="R25" t="n">
-        <v>6707591</v>
+        <v>6707500</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 14443-2025 artfynd.xlsx
+++ b/artfynd/A 14443-2025 artfynd.xlsx
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123965543</v>
+        <v>123968246</v>
       </c>
       <c r="B5" t="n">
-        <v>92271</v>
+        <v>57491</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,35 +1036,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1073,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507676</v>
+        <v>507683</v>
       </c>
       <c r="R5" t="n">
-        <v>6707387</v>
+        <v>6707604</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1108,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1118,12 +1114,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>G:a fk</t>
+          <t>Möjlig födosök tretåig.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123968246</v>
+        <v>123965543</v>
       </c>
       <c r="B6" t="n">
-        <v>57491</v>
+        <v>92271</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,31 +1158,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>507683</v>
+        <v>507676</v>
       </c>
       <c r="R6" t="n">
-        <v>6707604</v>
+        <v>6707387</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1240,12 +1240,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Möjlig födosök tretåig.</t>
+          <t>G:a fk</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 14443-2025 artfynd.xlsx
+++ b/artfynd/A 14443-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123966171</v>
+        <v>123965450</v>
       </c>
       <c r="B2" t="n">
-        <v>90955</v>
+        <v>78788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123982500</v>
+        <v>123967167</v>
       </c>
       <c r="B3" t="n">
         <v>56700</v>
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507842</v>
+        <v>507868</v>
       </c>
       <c r="R3" t="n">
-        <v>6707423</v>
+        <v>6707394</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Under äldre tall</t>
+          <t>Under tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,7 +912,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123968070</v>
+        <v>123982563</v>
       </c>
       <c r="B4" t="n">
         <v>78788</v>
@@ -946,16 +946,19 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Porsmyran. V, Dlr</t>
+          <t>Porsmyran V, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507735</v>
+        <v>507817</v>
       </c>
       <c r="R4" t="n">
-        <v>6707521</v>
+        <v>6707465</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -987,7 +990,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +1000,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,6 +1009,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1024,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123968246</v>
+        <v>123982555</v>
       </c>
       <c r="B5" t="n">
-        <v>57491</v>
+        <v>56700</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,43 +1040,54 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>dödad av predator</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Porsmyran. V, Dlr</t>
+          <t>Porsmyran V, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507683</v>
+        <v>507817</v>
       </c>
       <c r="R5" t="n">
-        <v>6707604</v>
+        <v>6707465</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,7 +1119,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,12 +1129,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Möjlig födosök tretåig.</t>
+          <t>Slagen tjäderhöna möjligen på tänkt bogrop intill tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1272,10 +1287,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123967723</v>
+        <v>123982500</v>
       </c>
       <c r="B7" t="n">
-        <v>57491</v>
+        <v>56700</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1284,43 +1299,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Porsmyran. V, Dlr</t>
+          <t>Porsmyran V, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507804</v>
+        <v>507842</v>
       </c>
       <c r="R7" t="n">
-        <v>6707453</v>
+        <v>6707423</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1352,7 +1370,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1362,7 +1380,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Under äldre tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1389,10 +1412,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123967232</v>
+        <v>123967723</v>
       </c>
       <c r="B8" t="n">
-        <v>78789</v>
+        <v>57491</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1405,34 +1428,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>230405</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Porsmyran. V, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507817</v>
+        <v>507804</v>
       </c>
       <c r="R8" t="n">
-        <v>6707436</v>
+        <v>6707453</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1464,7 +1492,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1474,7 +1502,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1494,17 +1522,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123967167</v>
+        <v>123967232</v>
       </c>
       <c r="B9" t="n">
-        <v>56700</v>
+        <v>78789</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1513,49 +1541,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>230405</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Porsmyran V, Dlr</t>
+          <t>Porsmyran. V, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507868</v>
+        <v>507817</v>
       </c>
       <c r="R9" t="n">
-        <v>6707394</v>
+        <v>6707436</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1584,7 +1604,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1594,12 +1614,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:22</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Under tall.</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1619,14 +1634,14 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123982563</v>
+        <v>123968187</v>
       </c>
       <c r="B10" t="n">
         <v>78788</v>
@@ -1660,19 +1675,16 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Porsmyran V, Dlr</t>
+          <t>Porsmyran. V, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>507817</v>
+        <v>507735</v>
       </c>
       <c r="R10" t="n">
-        <v>6707465</v>
+        <v>6707521</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1704,7 +1716,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1714,7 +1726,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1723,7 +1735,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1735,17 +1746,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123982555</v>
+        <v>123966171</v>
       </c>
       <c r="B11" t="n">
-        <v>56700</v>
+        <v>90955</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1758,50 +1769,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>dödad av predator</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Porsmyran V, Dlr</t>
+          <t>Porsmyran. V, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>507817</v>
+        <v>507676</v>
       </c>
       <c r="R11" t="n">
-        <v>6707465</v>
+        <v>6707387</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1833,7 +1828,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1843,12 +1838,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:40</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Slagen tjäderhöna möjligen på tänkt bogrop intill tall.</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1875,10 +1865,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123965450</v>
+        <v>123968246</v>
       </c>
       <c r="B12" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1891,34 +1881,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Porsmyran. V, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>507676</v>
+        <v>507683</v>
       </c>
       <c r="R12" t="n">
-        <v>6707387</v>
+        <v>6707604</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1950,7 +1945,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1960,7 +1955,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Möjlig födosök tretåig.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1987,7 +1987,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123996113</v>
+        <v>123996142</v>
       </c>
       <c r="B13" t="n">
         <v>78788</v>
@@ -2030,10 +2030,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>507774</v>
+        <v>507697</v>
       </c>
       <c r="R13" t="n">
-        <v>6707494</v>
+        <v>6707549</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -2093,7 +2093,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123995839</v>
+        <v>123995965</v>
       </c>
       <c r="B14" t="n">
         <v>78788</v>
@@ -2136,10 +2136,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>507890</v>
+        <v>507831</v>
       </c>
       <c r="R14" t="n">
-        <v>6707384</v>
+        <v>6707436</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2305,10 +2305,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123996079</v>
+        <v>123996113</v>
       </c>
       <c r="B16" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2317,39 +2317,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2357,10 +2348,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>507858</v>
+        <v>507774</v>
       </c>
       <c r="R16" t="n">
-        <v>6707444</v>
+        <v>6707494</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2420,7 +2411,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123996155</v>
+        <v>123995875</v>
       </c>
       <c r="B17" t="n">
         <v>78788</v>
@@ -2463,10 +2454,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>507675</v>
+        <v>507841</v>
       </c>
       <c r="R17" t="n">
-        <v>6707591</v>
+        <v>6707427</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2493,12 +2484,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2632,10 +2623,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123995953</v>
+        <v>123999506</v>
       </c>
       <c r="B19" t="n">
-        <v>78788</v>
+        <v>5176</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2644,44 +2635,50 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Porsmyran, Dlr</t>
+          <t>Porsmyran V, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>507837</v>
+        <v>507817</v>
       </c>
       <c r="R19" t="n">
-        <v>6707412</v>
+        <v>6707434</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2708,9 +2705,19 @@
           <t>2025-04-11</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2726,22 +2733,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123999506</v>
+        <v>123995839</v>
       </c>
       <c r="B20" t="n">
-        <v>5176</v>
+        <v>78788</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2750,50 +2757,44 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Porsmyran V, Dlr</t>
+          <t>Porsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>507817</v>
+        <v>507890</v>
       </c>
       <c r="R20" t="n">
-        <v>6707434</v>
+        <v>6707384</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2820,19 +2821,9 @@
           <t>2025-04-11</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2848,19 +2839,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123996142</v>
+        <v>123995953</v>
       </c>
       <c r="B21" t="n">
         <v>78788</v>
@@ -2903,10 +2894,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>507697</v>
+        <v>507837</v>
       </c>
       <c r="R21" t="n">
-        <v>6707549</v>
+        <v>6707412</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2966,10 +2957,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123995965</v>
+        <v>123996079</v>
       </c>
       <c r="B22" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2978,30 +2969,39 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3009,10 +3009,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>507831</v>
+        <v>507858</v>
       </c>
       <c r="R22" t="n">
-        <v>6707436</v>
+        <v>6707444</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -3178,7 +3178,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123995875</v>
+        <v>123996155</v>
       </c>
       <c r="B24" t="n">
         <v>78788</v>
@@ -3221,10 +3221,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>507841</v>
+        <v>507675</v>
       </c>
       <c r="R24" t="n">
-        <v>6707427</v>
+        <v>6707591</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-12</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 14443-2025 artfynd.xlsx
+++ b/artfynd/A 14443-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123982500</v>
+        <v>123967167</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507842</v>
+        <v>507868</v>
       </c>
       <c r="R3" t="n">
-        <v>6707423</v>
+        <v>6707394</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Under äldre tall</t>
+          <t>Under tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,7 +922,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123968187</v>
+        <v>123965450</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -962,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507735</v>
+        <v>507676</v>
       </c>
       <c r="R4" t="n">
-        <v>6707521</v>
+        <v>6707387</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -997,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,17 +1027,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123982555</v>
+        <v>123967232</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>78811</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,54 +1046,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>230405</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>dödad av predator</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Porsmyran V, Dlr</t>
+          <t>Porsmyran. V, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>507817</v>
       </c>
       <c r="R5" t="n">
-        <v>6707465</v>
+        <v>6707436</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1125,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1135,12 +1119,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:40</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Slagen tjäderhöna möjligen på tänkt bogrop intill tall.</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1160,17 +1139,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123967167</v>
+        <v>123982563</v>
       </c>
       <c r="B6" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1179,35 +1158,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1215,13 +1189,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>507868</v>
+        <v>507817</v>
       </c>
       <c r="R6" t="n">
-        <v>6707394</v>
+        <v>6707465</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1250,7 +1224,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1260,12 +1234,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:22</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Under tall.</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1274,6 +1243,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1292,10 +1262,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123965543</v>
+        <v>123968070</v>
       </c>
       <c r="B7" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1304,47 +1274,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Porsmyran. V, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507676</v>
+        <v>507735</v>
       </c>
       <c r="R7" t="n">
-        <v>6707387</v>
+        <v>6707521</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1376,7 +1337,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1386,12 +1347,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:37</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>G:a fk</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1418,10 +1374,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123966171</v>
+        <v>123967723</v>
       </c>
       <c r="B8" t="n">
-        <v>90977</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1430,38 +1386,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Porsmyran. V, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507676</v>
+        <v>507804</v>
       </c>
       <c r="R8" t="n">
-        <v>6707387</v>
+        <v>6707453</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1493,7 +1454,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1503,7 +1464,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1530,10 +1491,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123965450</v>
+        <v>123965543</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1542,28 +1503,37 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Porsmyran. V, Dlr</t>
@@ -1605,7 +1575,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1615,7 +1585,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>G:a fk</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1642,10 +1617,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123967232</v>
+        <v>123982500</v>
       </c>
       <c r="B10" t="n">
-        <v>78811</v>
+        <v>56722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1654,38 +1629,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>230405</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Porsmyran. V, Dlr</t>
+          <t>Porsmyran V, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>507817</v>
+        <v>507842</v>
       </c>
       <c r="R10" t="n">
-        <v>6707436</v>
+        <v>6707423</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1717,7 +1700,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1727,7 +1710,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Under äldre tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1747,17 +1735,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123982563</v>
+        <v>123966171</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1766,41 +1754,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Porsmyran V, Dlr</t>
+          <t>Porsmyran. V, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>507817</v>
+        <v>507676</v>
       </c>
       <c r="R11" t="n">
-        <v>6707465</v>
+        <v>6707387</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1832,7 +1817,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1842,7 +1827,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1851,7 +1836,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1870,10 +1854,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123967723</v>
+        <v>123982555</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1882,43 +1866,54 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>dödad av predator</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Porsmyran. V, Dlr</t>
+          <t>Porsmyran V, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>507804</v>
+        <v>507817</v>
       </c>
       <c r="R12" t="n">
-        <v>6707453</v>
+        <v>6707465</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1950,7 +1945,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1960,7 +1955,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Slagen tjäderhöna möjligen på tänkt bogrop intill tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1987,7 +1987,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123995965</v>
+        <v>123996155</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -2030,10 +2030,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>507831</v>
+        <v>507675</v>
       </c>
       <c r="R13" t="n">
-        <v>6707436</v>
+        <v>6707591</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -2060,12 +2060,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2093,7 +2093,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123996142</v>
+        <v>123996113</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -2136,10 +2136,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>507697</v>
+        <v>507774</v>
       </c>
       <c r="R14" t="n">
-        <v>6707549</v>
+        <v>6707494</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2199,10 +2199,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123995923</v>
+        <v>123999506</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>5176</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2211,44 +2211,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Porsmyran, Dlr</t>
+          <t>Porsmyran V, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>507824</v>
+        <v>507817</v>
       </c>
       <c r="R15" t="n">
-        <v>6707424</v>
+        <v>6707434</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2275,9 +2281,19 @@
           <t>2025-04-11</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2293,12 +2309,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2411,7 +2427,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123996131</v>
+        <v>123995839</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2454,10 +2470,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>507768</v>
+        <v>507890</v>
       </c>
       <c r="R17" t="n">
-        <v>6707485</v>
+        <v>6707384</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2517,7 +2533,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123996155</v>
+        <v>123996098</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2556,14 +2572,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Porsmyran, Dlr</t>
+          <t>Porsmyram, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>507675</v>
+        <v>507760</v>
       </c>
       <c r="R18" t="n">
-        <v>6707591</v>
+        <v>6707500</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2590,12 +2606,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2623,7 +2639,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123996113</v>
+        <v>123996142</v>
       </c>
       <c r="B19" t="n">
         <v>78810</v>
@@ -2666,10 +2682,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>507774</v>
+        <v>507697</v>
       </c>
       <c r="R19" t="n">
-        <v>6707494</v>
+        <v>6707549</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2729,7 +2745,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123995875</v>
+        <v>123996131</v>
       </c>
       <c r="B20" t="n">
         <v>78810</v>
@@ -2772,10 +2788,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>507841</v>
+        <v>507768</v>
       </c>
       <c r="R20" t="n">
-        <v>6707427</v>
+        <v>6707485</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2835,10 +2851,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123999506</v>
+        <v>123996079</v>
       </c>
       <c r="B21" t="n">
-        <v>5176</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2847,50 +2863,53 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Porsmyran V, Dlr</t>
+          <t>Porsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>507817</v>
+        <v>507858</v>
       </c>
       <c r="R21" t="n">
-        <v>6707434</v>
+        <v>6707444</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2917,19 +2936,9 @@
           <t>2025-04-11</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2945,19 +2954,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123995839</v>
+        <v>123995953</v>
       </c>
       <c r="B22" t="n">
         <v>78810</v>
@@ -3000,10 +3009,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>507890</v>
+        <v>507837</v>
       </c>
       <c r="R22" t="n">
-        <v>6707384</v>
+        <v>6707412</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -3063,7 +3072,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123996098</v>
+        <v>123995875</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -3102,14 +3111,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Porsmyram, Dlr</t>
+          <t>Porsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>507760</v>
+        <v>507841</v>
       </c>
       <c r="R23" t="n">
-        <v>6707500</v>
+        <v>6707427</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3169,7 +3178,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123995953</v>
+        <v>123995923</v>
       </c>
       <c r="B24" t="n">
         <v>78810</v>
@@ -3212,10 +3221,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>507837</v>
+        <v>507824</v>
       </c>
       <c r="R24" t="n">
-        <v>6707412</v>
+        <v>6707424</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3275,10 +3284,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123996079</v>
+        <v>123995965</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3287,39 +3296,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3327,10 +3327,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>507858</v>
+        <v>507831</v>
       </c>
       <c r="R25" t="n">
-        <v>6707444</v>
+        <v>6707436</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>

--- a/artfynd/A 14443-2025 artfynd.xlsx
+++ b/artfynd/A 14443-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123968246</v>
+        <v>123982500</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Porsmyran. V, Dlr</t>
+          <t>Porsmyran V, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>507683</v>
+        <v>507842</v>
       </c>
       <c r="R2" t="n">
-        <v>6707604</v>
+        <v>6707423</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +768,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Möjlig födosök tretåig.</t>
+          <t>Under äldre tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123967167</v>
+        <v>123966171</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>90977</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,45 +816,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Porsmyran V, Dlr</t>
+          <t>Porsmyran. V, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507868</v>
+        <v>507676</v>
       </c>
       <c r="R3" t="n">
-        <v>6707394</v>
+        <v>6707387</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,12 +885,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:22</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Under tall.</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,7 +912,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123965450</v>
+        <v>123982563</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -956,16 +946,19 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Porsmyran. V, Dlr</t>
+          <t>Porsmyran V, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507676</v>
+        <v>507817</v>
       </c>
       <c r="R4" t="n">
-        <v>6707387</v>
+        <v>6707465</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -997,7 +990,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,7 +1000,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,6 +1009,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1034,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123967232</v>
+        <v>123967167</v>
       </c>
       <c r="B5" t="n">
-        <v>78811</v>
+        <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,41 +1040,49 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>230405</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Porsmyran. V, Dlr</t>
+          <t>Porsmyran V, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507817</v>
+        <v>507868</v>
       </c>
       <c r="R5" t="n">
-        <v>6707436</v>
+        <v>6707394</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1109,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,7 +1121,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Under tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,17 +1146,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123982563</v>
+        <v>123982555</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,30 +1165,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>dödad av predator</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1224,7 +1244,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1234,7 +1254,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Slagen tjäderhöna möjligen på tänkt bogrop intill tall.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,7 +1268,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1262,7 +1286,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123968070</v>
+        <v>123965450</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1302,10 +1326,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507735</v>
+        <v>507676</v>
       </c>
       <c r="R7" t="n">
-        <v>6707521</v>
+        <v>6707387</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1337,7 +1361,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1347,7 +1371,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,10 +1398,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123967723</v>
+        <v>123968070</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1390,39 +1414,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Porsmyran. V, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507804</v>
+        <v>507735</v>
       </c>
       <c r="R8" t="n">
-        <v>6707453</v>
+        <v>6707521</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1454,7 +1473,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1464,7 +1483,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,10 +1510,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123965543</v>
+        <v>123967232</v>
       </c>
       <c r="B9" t="n">
-        <v>92293</v>
+        <v>78811</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,47 +1522,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>230405</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Porsmyran. V, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507676</v>
+        <v>507817</v>
       </c>
       <c r="R9" t="n">
-        <v>6707387</v>
+        <v>6707436</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1575,7 +1585,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1585,12 +1595,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:37</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>G:a fk</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1610,17 +1615,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123982500</v>
+        <v>123968246</v>
       </c>
       <c r="B10" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1629,46 +1634,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Porsmyran V, Dlr</t>
+          <t>Porsmyran. V, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>507842</v>
+        <v>507683</v>
       </c>
       <c r="R10" t="n">
-        <v>6707423</v>
+        <v>6707604</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1700,7 +1702,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1710,12 +1712,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Under äldre tall</t>
+          <t>Möjlig födosök tretåig.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1742,10 +1744,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123966171</v>
+        <v>123965543</v>
       </c>
       <c r="B11" t="n">
-        <v>90977</v>
+        <v>92293</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1758,24 +1760,33 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Porsmyran. V, Dlr</t>
@@ -1817,7 +1828,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1827,7 +1838,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>G:a fk</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1854,10 +1870,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123982555</v>
+        <v>123967723</v>
       </c>
       <c r="B12" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1866,54 +1882,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>dödad av predator</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Porsmyran V, Dlr</t>
+          <t>Porsmyran. V, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>507817</v>
+        <v>507804</v>
       </c>
       <c r="R12" t="n">
-        <v>6707465</v>
+        <v>6707453</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1945,7 +1950,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1955,12 +1960,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:40</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Slagen tjäderhöna möjligen på tänkt bogrop intill tall.</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1987,7 +1987,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123996155</v>
+        <v>123995953</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -2030,10 +2030,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>507675</v>
+        <v>507837</v>
       </c>
       <c r="R13" t="n">
-        <v>6707591</v>
+        <v>6707412</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -2060,12 +2060,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2093,7 +2093,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123996113</v>
+        <v>123996131</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -2136,10 +2136,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>507774</v>
+        <v>507768</v>
       </c>
       <c r="R14" t="n">
-        <v>6707494</v>
+        <v>6707485</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2199,10 +2199,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123999506</v>
+        <v>123995839</v>
       </c>
       <c r="B15" t="n">
-        <v>5176</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2211,50 +2211,44 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Porsmyran V, Dlr</t>
+          <t>Porsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>507817</v>
+        <v>507890</v>
       </c>
       <c r="R15" t="n">
-        <v>6707434</v>
+        <v>6707384</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2281,19 +2275,9 @@
           <t>2025-04-11</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>11:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2309,19 +2293,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123995815</v>
+        <v>123996098</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2360,14 +2344,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Porsmyran, Dlr</t>
+          <t>Porsmyram, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>507867</v>
+        <v>507760</v>
       </c>
       <c r="R16" t="n">
-        <v>6707382</v>
+        <v>6707500</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2427,10 +2411,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123995839</v>
+        <v>123996079</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2439,30 +2423,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2470,10 +2463,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>507890</v>
+        <v>507858</v>
       </c>
       <c r="R17" t="n">
-        <v>6707384</v>
+        <v>6707444</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2533,10 +2526,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123996098</v>
+        <v>123999506</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>5176</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2545,44 +2538,50 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Porsmyram, Dlr</t>
+          <t>Porsmyran V, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>507760</v>
+        <v>507817</v>
       </c>
       <c r="R18" t="n">
-        <v>6707500</v>
+        <v>6707434</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2609,9 +2608,19 @@
           <t>2025-04-11</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2627,19 +2636,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123996142</v>
+        <v>123995815</v>
       </c>
       <c r="B19" t="n">
         <v>78810</v>
@@ -2682,10 +2691,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>507697</v>
+        <v>507867</v>
       </c>
       <c r="R19" t="n">
-        <v>6707549</v>
+        <v>6707382</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2745,7 +2754,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123996131</v>
+        <v>123996155</v>
       </c>
       <c r="B20" t="n">
         <v>78810</v>
@@ -2788,10 +2797,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>507768</v>
+        <v>507675</v>
       </c>
       <c r="R20" t="n">
-        <v>6707485</v>
+        <v>6707591</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2818,12 +2827,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2851,10 +2860,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123996079</v>
+        <v>123995965</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2863,39 +2872,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2903,10 +2903,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>507858</v>
+        <v>507831</v>
       </c>
       <c r="R21" t="n">
-        <v>6707444</v>
+        <v>6707436</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2966,7 +2966,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123995953</v>
+        <v>123996142</v>
       </c>
       <c r="B22" t="n">
         <v>78810</v>
@@ -3009,10 +3009,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>507837</v>
+        <v>507697</v>
       </c>
       <c r="R22" t="n">
-        <v>6707412</v>
+        <v>6707549</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -3284,7 +3284,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123995965</v>
+        <v>123996113</v>
       </c>
       <c r="B25" t="n">
         <v>78810</v>
@@ -3327,10 +3327,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>507831</v>
+        <v>507774</v>
       </c>
       <c r="R25" t="n">
-        <v>6707436</v>
+        <v>6707494</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>

--- a/artfynd/A 14443-2025 artfynd.xlsx
+++ b/artfynd/A 14443-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123982500</v>
+        <v>123968187</v>
       </c>
       <c r="B2" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Porsmyran V, Dlr</t>
+          <t>Porsmyran. V, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>507842</v>
+        <v>507735</v>
       </c>
       <c r="R2" t="n">
-        <v>6707423</v>
+        <v>6707521</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -758,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Under äldre tall</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,17 +780,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123966171</v>
+        <v>123965543</v>
       </c>
       <c r="B3" t="n">
-        <v>90977</v>
+        <v>92293</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,24 +803,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Porsmyran. V, Dlr</t>
@@ -875,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,7 +881,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>G:a fk</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123982563</v>
+        <v>123968246</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,37 +929,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Porsmyran V, Dlr</t>
+          <t>Porsmyran. V, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507817</v>
+        <v>507683</v>
       </c>
       <c r="R4" t="n">
-        <v>6707465</v>
+        <v>6707604</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -990,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1000,7 +1003,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Möjlig födosök tretåig.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,7 +1017,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1028,7 +1035,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123967167</v>
+        <v>123982555</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1061,12 +1068,20 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>dödad av predator</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1076,13 +1091,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507868</v>
+        <v>507817</v>
       </c>
       <c r="R5" t="n">
-        <v>6707394</v>
+        <v>6707465</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1111,7 +1126,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,12 +1136,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Under tall.</t>
+          <t>Slagen tjäderhöna möjligen på tänkt bogrop intill tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,10 +1168,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123982555</v>
+        <v>123966171</v>
       </c>
       <c r="B6" t="n">
-        <v>56722</v>
+        <v>90977</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1169,50 +1184,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>dödad av predator</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Porsmyran V, Dlr</t>
+          <t>Porsmyran. V, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>507817</v>
+        <v>507676</v>
       </c>
       <c r="R6" t="n">
-        <v>6707465</v>
+        <v>6707387</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1244,7 +1243,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1254,12 +1253,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:40</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Slagen tjäderhöna möjligen på tänkt bogrop intill tall.</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1286,10 +1280,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123965450</v>
+        <v>123967723</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1302,34 +1296,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Porsmyran. V, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507676</v>
+        <v>507804</v>
       </c>
       <c r="R7" t="n">
-        <v>6707387</v>
+        <v>6707453</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1361,7 +1360,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1371,7 +1370,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1398,7 +1397,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123968070</v>
+        <v>123965450</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1438,10 +1437,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507735</v>
+        <v>507676</v>
       </c>
       <c r="R8" t="n">
-        <v>6707521</v>
+        <v>6707387</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1473,7 +1472,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1483,7 +1482,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1510,10 +1509,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123967232</v>
+        <v>123967167</v>
       </c>
       <c r="B9" t="n">
-        <v>78811</v>
+        <v>56722</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1522,41 +1521,49 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>230405</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Porsmyran. V, Dlr</t>
+          <t>Porsmyran V, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507817</v>
+        <v>507868</v>
       </c>
       <c r="R9" t="n">
-        <v>6707436</v>
+        <v>6707394</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1585,7 +1592,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1595,7 +1602,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Under tall.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1615,17 +1627,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123968246</v>
+        <v>123982563</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1638,39 +1650,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Porsmyran. V, Dlr</t>
+          <t>Porsmyran V, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>507683</v>
+        <v>507817</v>
       </c>
       <c r="R10" t="n">
-        <v>6707604</v>
+        <v>6707465</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1702,7 +1712,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1712,12 +1722,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Möjlig födosök tretåig.</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1726,6 +1731,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1744,10 +1750,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123965543</v>
+        <v>123982500</v>
       </c>
       <c r="B11" t="n">
-        <v>92293</v>
+        <v>56722</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1760,43 +1766,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Porsmyran. V, Dlr</t>
+          <t>Porsmyran V, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>507676</v>
+        <v>507842</v>
       </c>
       <c r="R11" t="n">
-        <v>6707387</v>
+        <v>6707423</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1828,7 +1833,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1838,12 +1843,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>G:a fk</t>
+          <t>Under äldre tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1870,10 +1875,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123967723</v>
+        <v>123967232</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>78811</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1886,39 +1891,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>230405</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Porsmyran. V, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>507804</v>
+        <v>507817</v>
       </c>
       <c r="R12" t="n">
-        <v>6707453</v>
+        <v>6707436</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1980,17 +1980,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123995953</v>
+        <v>123999506</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>5176</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1999,44 +1999,50 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Porsmyran, Dlr</t>
+          <t>Porsmyran V, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>507837</v>
+        <v>507817</v>
       </c>
       <c r="R13" t="n">
-        <v>6707412</v>
+        <v>6707434</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2063,9 +2069,19 @@
           <t>2025-04-11</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2081,19 +2097,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123996131</v>
+        <v>123996142</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -2136,10 +2152,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>507768</v>
+        <v>507697</v>
       </c>
       <c r="R14" t="n">
-        <v>6707485</v>
+        <v>6707549</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2199,7 +2215,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123995839</v>
+        <v>123995953</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2242,10 +2258,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>507890</v>
+        <v>507837</v>
       </c>
       <c r="R15" t="n">
-        <v>6707384</v>
+        <v>6707412</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2305,7 +2321,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123996098</v>
+        <v>123995875</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2344,14 +2360,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Porsmyram, Dlr</t>
+          <t>Porsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>507760</v>
+        <v>507841</v>
       </c>
       <c r="R16" t="n">
-        <v>6707500</v>
+        <v>6707427</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2411,10 +2427,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123996079</v>
+        <v>123995965</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2423,39 +2439,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2463,10 +2470,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>507858</v>
+        <v>507831</v>
       </c>
       <c r="R17" t="n">
-        <v>6707444</v>
+        <v>6707436</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2526,10 +2533,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123999506</v>
+        <v>123996155</v>
       </c>
       <c r="B18" t="n">
-        <v>5176</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2538,50 +2545,44 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Porsmyran V, Dlr</t>
+          <t>Porsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>507817</v>
+        <v>507675</v>
       </c>
       <c r="R18" t="n">
-        <v>6707434</v>
+        <v>6707591</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2605,22 +2606,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2025-04-12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2025-04-12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2636,19 +2627,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123995815</v>
+        <v>123995923</v>
       </c>
       <c r="B19" t="n">
         <v>78810</v>
@@ -2691,10 +2682,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>507867</v>
+        <v>507824</v>
       </c>
       <c r="R19" t="n">
-        <v>6707382</v>
+        <v>6707424</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2754,7 +2745,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123996155</v>
+        <v>123995839</v>
       </c>
       <c r="B20" t="n">
         <v>78810</v>
@@ -2797,10 +2788,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>507675</v>
+        <v>507890</v>
       </c>
       <c r="R20" t="n">
-        <v>6707591</v>
+        <v>6707384</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2827,12 +2818,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2860,7 +2851,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123995965</v>
+        <v>123996098</v>
       </c>
       <c r="B21" t="n">
         <v>78810</v>
@@ -2899,14 +2890,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Porsmyran, Dlr</t>
+          <t>Porsmyram, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>507831</v>
+        <v>507760</v>
       </c>
       <c r="R21" t="n">
-        <v>6707436</v>
+        <v>6707500</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2966,10 +2957,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123996142</v>
+        <v>123996079</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2978,30 +2969,39 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3009,10 +3009,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>507697</v>
+        <v>507858</v>
       </c>
       <c r="R22" t="n">
-        <v>6707549</v>
+        <v>6707444</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -3072,7 +3072,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123995875</v>
+        <v>123995815</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -3115,10 +3115,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>507841</v>
+        <v>507867</v>
       </c>
       <c r="R23" t="n">
-        <v>6707427</v>
+        <v>6707382</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3178,7 +3178,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123995923</v>
+        <v>123996131</v>
       </c>
       <c r="B24" t="n">
         <v>78810</v>
@@ -3221,10 +3221,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>507824</v>
+        <v>507768</v>
       </c>
       <c r="R24" t="n">
-        <v>6707424</v>
+        <v>6707485</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>

--- a/artfynd/A 14443-2025 artfynd.xlsx
+++ b/artfynd/A 14443-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123968187</v>
+        <v>123968246</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Porsmyran. V, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>507735</v>
+        <v>507683</v>
       </c>
       <c r="R2" t="n">
-        <v>6707521</v>
+        <v>6707604</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Möjlig födosök tretåig.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,17 +790,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123965543</v>
+        <v>123982555</v>
       </c>
       <c r="B3" t="n">
-        <v>92293</v>
+        <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,43 +813,50 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>dödad av predator</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Porsmyran. V, Dlr</t>
+          <t>Porsmyran V, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507676</v>
+        <v>507817</v>
       </c>
       <c r="R3" t="n">
-        <v>6707387</v>
+        <v>6707465</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,7 +888,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,12 +898,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>G:a fk</t>
+          <t>Slagen tjäderhöna möjligen på tänkt bogrop intill tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +930,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123968246</v>
+        <v>123982563</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,39 +946,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Porsmyran. V, Dlr</t>
+          <t>Porsmyran V, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507683</v>
+        <v>507817</v>
       </c>
       <c r="R4" t="n">
-        <v>6707604</v>
+        <v>6707465</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,7 +1008,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,12 +1018,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Möjlig födosök tretåig.</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,6 +1027,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1035,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123982555</v>
+        <v>123968187</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,54 +1058,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>dödad av predator</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Porsmyran V, Dlr</t>
+          <t>Porsmyran. V, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507817</v>
+        <v>507735</v>
       </c>
       <c r="R5" t="n">
-        <v>6707465</v>
+        <v>6707521</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1126,7 +1121,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1136,12 +1131,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:40</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Slagen tjäderhöna möjligen på tänkt bogrop intill tall.</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1161,17 +1151,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123966171</v>
+        <v>123967167</v>
       </c>
       <c r="B6" t="n">
-        <v>90977</v>
+        <v>56722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1184,37 +1174,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Porsmyran. V, Dlr</t>
+          <t>Porsmyran V, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>507676</v>
+        <v>507868</v>
       </c>
       <c r="R6" t="n">
-        <v>6707387</v>
+        <v>6707394</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1243,7 +1241,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1253,7 +1251,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Under tall.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,10 +1283,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123967723</v>
+        <v>123966171</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>90977</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1292,43 +1295,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Porsmyran. V, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507804</v>
+        <v>507676</v>
       </c>
       <c r="R7" t="n">
-        <v>6707453</v>
+        <v>6707387</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1360,7 +1358,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1370,7 +1368,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1397,10 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123965450</v>
+        <v>123967232</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>78811</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1413,16 +1411,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1437,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507676</v>
+        <v>507817</v>
       </c>
       <c r="R8" t="n">
-        <v>6707387</v>
+        <v>6707436</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1472,7 +1470,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1482,7 +1480,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1502,17 +1500,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123967167</v>
+        <v>123967723</v>
       </c>
       <c r="B9" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1521,49 +1519,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Porsmyran V, Dlr</t>
+          <t>Porsmyran. V, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507868</v>
+        <v>507804</v>
       </c>
       <c r="R9" t="n">
-        <v>6707394</v>
+        <v>6707453</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1592,7 +1587,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1602,12 +1597,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:22</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Under tall.</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1634,7 +1624,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123982563</v>
+        <v>123965450</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1668,19 +1658,16 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Porsmyran V, Dlr</t>
+          <t>Porsmyran. V, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>507817</v>
+        <v>507676</v>
       </c>
       <c r="R10" t="n">
-        <v>6707465</v>
+        <v>6707387</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1712,7 +1699,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1722,7 +1709,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1731,7 +1718,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1750,10 +1736,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123982500</v>
+        <v>123965543</v>
       </c>
       <c r="B11" t="n">
-        <v>56722</v>
+        <v>92293</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1766,42 +1752,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Porsmyran V, Dlr</t>
+          <t>Porsmyran. V, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>507842</v>
+        <v>507676</v>
       </c>
       <c r="R11" t="n">
-        <v>6707423</v>
+        <v>6707387</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1833,7 +1820,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1843,12 +1830,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Under äldre tall</t>
+          <t>G:a fk</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1875,10 +1862,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123967232</v>
+        <v>123982500</v>
       </c>
       <c r="B12" t="n">
-        <v>78811</v>
+        <v>56722</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1887,38 +1874,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>230405</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Porsmyran. V, Dlr</t>
+          <t>Porsmyran V, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>507817</v>
+        <v>507842</v>
       </c>
       <c r="R12" t="n">
-        <v>6707436</v>
+        <v>6707423</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1950,7 +1945,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1960,7 +1955,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Under äldre tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1980,17 +1980,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123999506</v>
+        <v>123996113</v>
       </c>
       <c r="B13" t="n">
-        <v>5176</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1999,50 +1999,44 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Porsmyran V, Dlr</t>
+          <t>Porsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>507817</v>
+        <v>507774</v>
       </c>
       <c r="R13" t="n">
-        <v>6707434</v>
+        <v>6707494</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2069,19 +2063,9 @@
           <t>2025-04-11</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2097,19 +2081,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123996142</v>
+        <v>123995839</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -2152,10 +2136,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>507697</v>
+        <v>507890</v>
       </c>
       <c r="R14" t="n">
-        <v>6707549</v>
+        <v>6707384</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2215,10 +2199,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123995953</v>
+        <v>123999506</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>5176</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2227,44 +2211,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Porsmyran, Dlr</t>
+          <t>Porsmyran V, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>507837</v>
+        <v>507817</v>
       </c>
       <c r="R15" t="n">
-        <v>6707412</v>
+        <v>6707434</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2291,9 +2281,19 @@
           <t>2025-04-11</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2309,19 +2309,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123995875</v>
+        <v>123995815</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>507841</v>
+        <v>507867</v>
       </c>
       <c r="R16" t="n">
-        <v>6707427</v>
+        <v>6707382</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2427,7 +2427,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123995965</v>
+        <v>123995923</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>507831</v>
+        <v>507824</v>
       </c>
       <c r="R17" t="n">
-        <v>6707436</v>
+        <v>6707424</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2533,7 +2533,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123996155</v>
+        <v>123995953</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2576,10 +2576,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>507675</v>
+        <v>507837</v>
       </c>
       <c r="R18" t="n">
-        <v>6707591</v>
+        <v>6707412</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2606,12 +2606,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2639,7 +2639,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123995923</v>
+        <v>123996098</v>
       </c>
       <c r="B19" t="n">
         <v>78810</v>
@@ -2678,14 +2678,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Porsmyran, Dlr</t>
+          <t>Porsmyram, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>507824</v>
+        <v>507760</v>
       </c>
       <c r="R19" t="n">
-        <v>6707424</v>
+        <v>6707500</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2745,7 +2745,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123995839</v>
+        <v>123995875</v>
       </c>
       <c r="B20" t="n">
         <v>78810</v>
@@ -2788,10 +2788,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>507890</v>
+        <v>507841</v>
       </c>
       <c r="R20" t="n">
-        <v>6707384</v>
+        <v>6707427</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2851,7 +2851,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123996098</v>
+        <v>123996155</v>
       </c>
       <c r="B21" t="n">
         <v>78810</v>
@@ -2890,14 +2890,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Porsmyram, Dlr</t>
+          <t>Porsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>507760</v>
+        <v>507675</v>
       </c>
       <c r="R21" t="n">
-        <v>6707500</v>
+        <v>6707591</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2924,12 +2924,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3072,7 +3072,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123995815</v>
+        <v>123996142</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -3115,10 +3115,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>507867</v>
+        <v>507697</v>
       </c>
       <c r="R23" t="n">
-        <v>6707382</v>
+        <v>6707549</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3284,7 +3284,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123996113</v>
+        <v>123995965</v>
       </c>
       <c r="B25" t="n">
         <v>78810</v>
@@ -3327,10 +3327,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>507774</v>
+        <v>507831</v>
       </c>
       <c r="R25" t="n">
-        <v>6707494</v>
+        <v>6707436</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>

--- a/artfynd/A 14443-2025 artfynd.xlsx
+++ b/artfynd/A 14443-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123968246</v>
+        <v>123968187</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Porsmyran. V, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>507683</v>
+        <v>507735</v>
       </c>
       <c r="R2" t="n">
-        <v>6707604</v>
+        <v>6707521</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Möjlig födosök tretåig.</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,17 +780,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123982555</v>
+        <v>123967232</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>78811</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,54 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>230405</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>dödad av predator</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Porsmyran V, Dlr</t>
+          <t>Porsmyran. V, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>507817</v>
       </c>
       <c r="R3" t="n">
-        <v>6707465</v>
+        <v>6707436</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -888,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -898,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:40</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Slagen tjäderhöna möjligen på tänkt bogrop intill tall.</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,17 +892,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123982563</v>
+        <v>123967167</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -942,30 +911,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -973,13 +947,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507817</v>
+        <v>507868</v>
       </c>
       <c r="R4" t="n">
-        <v>6707465</v>
+        <v>6707394</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1008,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1018,7 +992,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Under tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,7 +1006,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1046,7 +1024,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123968187</v>
+        <v>123965450</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1086,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507735</v>
+        <v>507676</v>
       </c>
       <c r="R5" t="n">
-        <v>6707521</v>
+        <v>6707387</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1121,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1131,7 +1109,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,17 +1129,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123967167</v>
+        <v>123967723</v>
       </c>
       <c r="B6" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,49 +1148,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Porsmyran V, Dlr</t>
+          <t>Porsmyran. V, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>507868</v>
+        <v>507804</v>
       </c>
       <c r="R6" t="n">
-        <v>6707394</v>
+        <v>6707453</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1241,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1251,12 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:22</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Under tall.</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1283,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123966171</v>
+        <v>123982555</v>
       </c>
       <c r="B7" t="n">
-        <v>90977</v>
+        <v>56722</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1299,34 +1269,50 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>dödad av predator</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Porsmyran. V, Dlr</t>
+          <t>Porsmyran V, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507676</v>
+        <v>507817</v>
       </c>
       <c r="R7" t="n">
-        <v>6707387</v>
+        <v>6707465</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1358,7 +1344,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1368,7 +1354,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Slagen tjäderhöna möjligen på tänkt bogrop intill tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1395,10 +1386,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123967232</v>
+        <v>123966171</v>
       </c>
       <c r="B8" t="n">
-        <v>78811</v>
+        <v>90977</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1407,25 +1398,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>230405</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1435,10 +1426,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507817</v>
+        <v>507676</v>
       </c>
       <c r="R8" t="n">
-        <v>6707436</v>
+        <v>6707387</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1470,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1480,7 +1471,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1500,14 +1491,14 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123967723</v>
+        <v>123968246</v>
       </c>
       <c r="B9" t="n">
         <v>57513</v>
@@ -1552,10 +1543,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507804</v>
+        <v>507683</v>
       </c>
       <c r="R9" t="n">
-        <v>6707453</v>
+        <v>6707604</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1598,6 +1589,11 @@
       <c r="AB9" t="inlineStr">
         <is>
           <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Möjlig födosök tretåig.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1624,10 +1620,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123965450</v>
+        <v>123965543</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1636,28 +1632,37 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Porsmyran. V, Dlr</t>
@@ -1699,7 +1704,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1709,7 +1714,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>G:a fk</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1736,10 +1746,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123965543</v>
+        <v>123982563</v>
       </c>
       <c r="B11" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1748,47 +1758,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Porsmyran. V, Dlr</t>
+          <t>Porsmyran V, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>507676</v>
+        <v>507817</v>
       </c>
       <c r="R11" t="n">
-        <v>6707387</v>
+        <v>6707465</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1820,7 +1824,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1830,12 +1834,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:37</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>G:a fk</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1844,6 +1843,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1987,10 +1987,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123996113</v>
+        <v>123996079</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1999,30 +1999,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2030,10 +2039,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>507774</v>
+        <v>507858</v>
       </c>
       <c r="R13" t="n">
-        <v>6707494</v>
+        <v>6707444</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -2093,7 +2102,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123995839</v>
+        <v>123995875</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -2136,10 +2145,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>507890</v>
+        <v>507841</v>
       </c>
       <c r="R14" t="n">
-        <v>6707384</v>
+        <v>6707427</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2199,10 +2208,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123999506</v>
+        <v>123995839</v>
       </c>
       <c r="B15" t="n">
-        <v>5176</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2211,50 +2220,44 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Porsmyran V, Dlr</t>
+          <t>Porsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>507817</v>
+        <v>507890</v>
       </c>
       <c r="R15" t="n">
-        <v>6707434</v>
+        <v>6707384</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2281,19 +2284,9 @@
           <t>2025-04-11</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>11:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2309,19 +2302,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123995815</v>
+        <v>123996098</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2360,14 +2353,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Porsmyran, Dlr</t>
+          <t>Porsmyram, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>507867</v>
+        <v>507760</v>
       </c>
       <c r="R16" t="n">
-        <v>6707382</v>
+        <v>6707500</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2427,7 +2420,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123995923</v>
+        <v>123996113</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2470,10 +2463,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>507824</v>
+        <v>507774</v>
       </c>
       <c r="R17" t="n">
-        <v>6707424</v>
+        <v>6707494</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2533,7 +2526,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123995953</v>
+        <v>123996155</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2576,10 +2569,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>507837</v>
+        <v>507675</v>
       </c>
       <c r="R18" t="n">
-        <v>6707412</v>
+        <v>6707591</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2606,12 +2599,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2639,10 +2632,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123996098</v>
+        <v>123999506</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>5176</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2651,44 +2644,50 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Porsmyram, Dlr</t>
+          <t>Porsmyran V, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>507760</v>
+        <v>507817</v>
       </c>
       <c r="R19" t="n">
-        <v>6707500</v>
+        <v>6707434</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2715,9 +2714,19 @@
           <t>2025-04-11</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2733,19 +2742,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123995875</v>
+        <v>123996131</v>
       </c>
       <c r="B20" t="n">
         <v>78810</v>
@@ -2788,10 +2797,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>507841</v>
+        <v>507768</v>
       </c>
       <c r="R20" t="n">
-        <v>6707427</v>
+        <v>6707485</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2851,7 +2860,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123996155</v>
+        <v>123995953</v>
       </c>
       <c r="B21" t="n">
         <v>78810</v>
@@ -2894,10 +2903,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>507675</v>
+        <v>507837</v>
       </c>
       <c r="R21" t="n">
-        <v>6707591</v>
+        <v>6707412</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2924,12 +2933,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2957,10 +2966,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123996079</v>
+        <v>123995965</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2969,39 +2978,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3009,10 +3009,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>507858</v>
+        <v>507831</v>
       </c>
       <c r="R22" t="n">
-        <v>6707444</v>
+        <v>6707436</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -3072,7 +3072,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123996142</v>
+        <v>123995815</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -3115,10 +3115,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>507697</v>
+        <v>507867</v>
       </c>
       <c r="R23" t="n">
-        <v>6707549</v>
+        <v>6707382</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3178,7 +3178,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123996131</v>
+        <v>123995923</v>
       </c>
       <c r="B24" t="n">
         <v>78810</v>
@@ -3221,10 +3221,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>507768</v>
+        <v>507824</v>
       </c>
       <c r="R24" t="n">
-        <v>6707485</v>
+        <v>6707424</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3284,7 +3284,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123995965</v>
+        <v>123996142</v>
       </c>
       <c r="B25" t="n">
         <v>78810</v>
@@ -3327,10 +3327,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>507831</v>
+        <v>507697</v>
       </c>
       <c r="R25" t="n">
-        <v>6707436</v>
+        <v>6707549</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>

--- a/artfynd/A 14443-2025 artfynd.xlsx
+++ b/artfynd/A 14443-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123967232</v>
+        <v>123967167</v>
       </c>
       <c r="B3" t="n">
-        <v>78811</v>
+        <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,41 +799,49 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>230405</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Porsmyran. V, Dlr</t>
+          <t>Porsmyran V, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507817</v>
+        <v>507868</v>
       </c>
       <c r="R3" t="n">
-        <v>6707436</v>
+        <v>6707394</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +880,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Under tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,17 +905,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123967167</v>
+        <v>123967232</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>78811</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,49 +924,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>230405</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Porsmyran V, Dlr</t>
+          <t>Porsmyran. V, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507868</v>
+        <v>507817</v>
       </c>
       <c r="R4" t="n">
-        <v>6707394</v>
+        <v>6707436</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,12 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:22</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Under tall.</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123996079</v>
+        <v>123995875</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1999,39 +1999,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2039,10 +2030,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>507858</v>
+        <v>507841</v>
       </c>
       <c r="R13" t="n">
-        <v>6707444</v>
+        <v>6707427</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -2102,10 +2093,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123995875</v>
+        <v>123996079</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2114,30 +2105,39 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2145,10 +2145,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>507841</v>
+        <v>507858</v>
       </c>
       <c r="R14" t="n">
-        <v>6707427</v>
+        <v>6707444</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>

--- a/artfynd/A 14443-2025 artfynd.xlsx
+++ b/artfynd/A 14443-2025 artfynd.xlsx
@@ -1987,10 +1987,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123995875</v>
+        <v>123996079</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1999,30 +1999,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2030,10 +2039,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>507841</v>
+        <v>507858</v>
       </c>
       <c r="R13" t="n">
-        <v>6707427</v>
+        <v>6707444</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -2093,10 +2102,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123996079</v>
+        <v>123995875</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2105,39 +2114,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2145,10 +2145,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>507858</v>
+        <v>507841</v>
       </c>
       <c r="R14" t="n">
-        <v>6707444</v>
+        <v>6707427</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
